--- a/Assessment Questions/AIE/DBM-120/Database Introduction/Overview and Key concepts of database management/Overview_DB_Proctoring.xlsx
+++ b/Assessment Questions/AIE/DBM-120/Database Introduction/Overview and Key concepts of database management/Overview_DB_Proctoring.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,9 +437,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -453,9 +450,6 @@
           <t>(dept_id INT, dept_name VARCHAR)</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -632,6 +626,11 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>Write Query</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
